--- a/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/SEO_QA_REV_R001.xlsx
+++ b/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/SEO_QA_REV_R001.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -471,12 +471,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>prompt_qa.md v1.0 / prompt.md v2.4</t>
+          <t>prompt_qa.md v1.0</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Project QA rubric used for R001 re-QA.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
@@ -493,116 +493,110 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Unique QA run folder.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>qa_batch_id</t>
+          <t>source_workbook</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>REV_R001</t>
+          <t>/Users/buiquanghuy/Documents/seo_chillgen/resutls/chillgen.com/chillgen_20260907_01/revisions/R001/SEO_Product_Optimization_revision_R001.xlsx</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Revision QA scope.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>shop_domain</t>
+          <t>source_workbook_sha256</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com</t>
+          <t>97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Shop domain.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>run_id</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>chillgen_20260907_01</t>
-        </is>
+          <t>scope_product_count</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Research run id.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>/Users/buiquanghuy/Documents/seo_chillgen/resutls/chillgen.com/chillgen_20260907_01/revisions/R001/SEO_Product_Optimization_revision_R001.xlsx</t>
-        </is>
+          <t>scope_image_count</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Frozen revision workbook being scored.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256</t>
+          <t>batch_status</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97</t>
+          <t>QA_PASS</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hash of frozen workbook at QA time.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>checked_at</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08T00:40:18+07:00</t>
-        </is>
+          <t>batch_final_score</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>97.5</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>QA report generation time Asia/Ho_Chi_Minh.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>scope_product_count</t>
+          <t>QA_PASS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -610,208 +604,69 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Only R001 product keys were scored.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>scope_image_count</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Image rows checked for scoped products.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>batch_final_score</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Average score across all scoped products.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>batch_status</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>QA_PASS</t>
-        </is>
+          <t>QA_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Batch passes only when every product is QA_PASS.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>10</v>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_APPROVED_NOT_DEPLOYED</t>
+        </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Products meeting &gt;=85, full coverage, no CRITICAL/MAJOR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>QA_REVISE</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Products requiring revision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QA_FAIL</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Products with critical/failing score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>QA_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Products missing enough evidence for final score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>critical_issues</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Critical issue count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>major_issues</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Major issue count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>minor_issues</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Minor issue count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>limitations</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Limitations retained for reviewer/deploy prerequisites.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>important_limitations</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SERP-only/no-volume keyword evidence; admin/export reconciliation still required before approval/deploy.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>These do not block content QA_PASS but block deployment readiness.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>approval_status</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>NOT_APPROVED_NOT_DEPLOYED</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>QA_PASS is not human approval and does not authorize Shopify changes.</t>
+          <t>Evidence-driven re-QA; blank final score means insufficient evidence.</t>
         </is>
       </c>
     </row>
@@ -847,7 +702,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="70" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -1014,14 +869,10 @@
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L001; R001-QA-L002</t>
-        </is>
-      </c>
+      <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1091,14 +942,10 @@
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L003; R001-QA-L004</t>
-        </is>
-      </c>
+      <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1015,10 @@
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L005; R001-QA-L006</t>
-        </is>
-      </c>
+      <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1245,14 +1088,10 @@
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L007; R001-QA-L008</t>
-        </is>
-      </c>
+      <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1322,14 +1161,10 @@
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L009; R001-QA-L010</t>
-        </is>
-      </c>
+      <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1234,10 @@
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L011; R001-QA-L012</t>
-        </is>
-      </c>
+      <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1476,14 +1307,10 @@
       <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L013; R001-QA-L014</t>
-        </is>
-      </c>
+      <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1553,14 +1380,10 @@
       <c r="Q9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L015; R001-QA-L016</t>
-        </is>
-      </c>
+      <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1453,10 @@
       <c r="Q10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L017; R001-QA-L018</t>
-        </is>
-      </c>
+      <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1707,14 +1526,10 @@
       <c r="Q11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L019; R001-QA-L020</t>
-        </is>
-      </c>
+      <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1557,7 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1829,12 +1644,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -1871,12 +1686,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -1913,12 +1728,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -1955,12 +1770,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1997,19 +1812,15 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L001; R001-QA-L002</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2043,12 +1854,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (52 chars).</t>
+          <t>meta_title_seo length=52; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -2085,12 +1896,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (52 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -2127,12 +1938,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (124 chars).</t>
+          <t>meta_description_seo length=124.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -2169,12 +1980,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -2187,15 +1998,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2204,19 +2015,19 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Derived from 8 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -2229,11 +2040,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2246,26 +2057,22 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L001; R001-QA-L002</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2299,12 +2106,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -2341,12 +2148,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -2383,12 +2190,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -2425,12 +2232,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -2467,19 +2274,15 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L003; R001-QA-L004</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2513,12 +2316,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (52 chars).</t>
+          <t>meta_title_seo length=52; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2555,12 +2358,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (52 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2597,12 +2400,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (110 chars).</t>
+          <t>meta_description_seo length=110.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2639,12 +2442,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -2657,15 +2460,15 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2674,19 +2477,19 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Derived from 16 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -2699,11 +2502,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -2716,26 +2519,22 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L003; R001-QA-L004</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2769,12 +2568,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -2811,12 +2610,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -2853,12 +2652,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -2895,12 +2694,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -2937,19 +2736,15 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L005; R001-QA-L006</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2983,12 +2778,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (54 chars).</t>
+          <t>meta_title_seo length=54; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -3025,12 +2820,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (54 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -3067,12 +2862,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (107 chars).</t>
+          <t>meta_description_seo length=107.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -3109,12 +2904,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -3127,15 +2922,15 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3144,19 +2939,19 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -3169,11 +2964,11 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
@@ -3186,26 +2981,22 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L005; R001-QA-L006</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3239,12 +3030,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -3281,12 +3072,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -3323,12 +3114,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -3365,12 +3156,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -3407,19 +3198,15 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L007; R001-QA-L008</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3453,12 +3240,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (56 chars).</t>
+          <t>meta_title_seo length=51; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -3495,12 +3282,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (56 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -3537,12 +3324,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (114 chars).</t>
+          <t>meta_description_seo length=114.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -3579,12 +3366,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -3597,15 +3384,15 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3614,19 +3401,19 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -3639,11 +3426,11 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
@@ -3656,26 +3443,22 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L007; R001-QA-L008</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3709,12 +3492,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -3751,12 +3534,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -3793,12 +3576,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -3835,12 +3618,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -3877,19 +3660,15 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L009; R001-QA-L010</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3923,12 +3702,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (57 chars).</t>
+          <t>meta_title_seo length=57; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -3965,12 +3744,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (57 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -4007,12 +3786,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (107 chars).</t>
+          <t>meta_description_seo length=107.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -4049,12 +3828,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -4067,15 +3846,15 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4084,19 +3863,19 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -4109,11 +3888,11 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
@@ -4126,26 +3905,22 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L009; R001-QA-L010</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4179,12 +3954,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -4221,12 +3996,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -4263,12 +4038,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -4305,12 +4080,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -4347,19 +4122,15 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L011; R001-QA-L012</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4393,12 +4164,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (52 chars).</t>
+          <t>meta_title_seo length=52; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -4435,12 +4206,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (52 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -4477,12 +4248,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (117 chars).</t>
+          <t>meta_description_seo length=117.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -4519,12 +4290,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -4537,15 +4308,15 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4554,19 +4325,19 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -4579,11 +4350,11 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -4596,26 +4367,22 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L011; R001-QA-L012</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4649,12 +4416,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -4691,12 +4458,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -4733,12 +4500,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -4775,12 +4542,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -4817,19 +4584,15 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L013; R001-QA-L014</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4863,12 +4626,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (53 chars).</t>
+          <t>meta_title_seo length=53; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -4905,12 +4668,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (53 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -4947,12 +4710,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (109 chars).</t>
+          <t>meta_description_seo length=109.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -4989,12 +4752,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -5007,15 +4770,15 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5024,19 +4787,19 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -5049,11 +4812,11 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
@@ -5066,26 +4829,22 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L013; R001-QA-L014</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5119,12 +4878,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -5161,12 +4920,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -5203,12 +4962,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -5245,12 +5004,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -5287,19 +5046,15 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L015; R001-QA-L016</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5333,12 +5088,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (60 chars).</t>
+          <t>meta_title_seo length=60; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -5375,12 +5130,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (60 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -5417,12 +5172,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (107 chars).</t>
+          <t>meta_description_seo length=107.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -5459,12 +5214,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -5477,15 +5232,15 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5494,19 +5249,19 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -5519,11 +5274,11 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
@@ -5536,26 +5291,22 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L015; R001-QA-L016</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5589,12 +5340,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -5631,12 +5382,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -5673,12 +5424,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -5715,12 +5466,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -5757,19 +5508,15 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L017; R001-QA-L018</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5803,12 +5550,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (56 chars).</t>
+          <t>meta_title_seo length=56; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -5845,12 +5592,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (56 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -5887,12 +5634,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (102 chars).</t>
+          <t>meta_description_seo length=102.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -5929,12 +5676,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -5947,15 +5694,15 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5964,19 +5711,19 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Derived from 5 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -5989,11 +5736,11 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
@@ -6006,26 +5753,22 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L017; R001-QA-L018</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6059,12 +5802,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Product type, visual motif, shape and theme in the revised copy match the page/live evidence and contact sheet.</t>
+          <t>Product identity is checked only when product type and verified facts are present.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -6101,12 +5844,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>R001 proposed fields are conservative and avoid unsupported outdoor/surface-performance claims targeted by the rerun.</t>
+          <t>Claims are checked against verified_product_facts and source excerpt.</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -6143,12 +5886,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Long-tail target is specific to the product design and avoids broad generic rug keywords.</t>
+          <t>Derived from this product's Keyword_Map rows; no keyword is assumed from title text.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -6185,12 +5928,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Workbook records product/marketplace SERP fit for product-page intent.</t>
+          <t>SERP fit is credited only when representative SERP references exist.</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -6227,19 +5970,15 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Evidence is disclosed as SERP-only/no-volume; usable for hypothesis-led SEO but not proof of search volume.</t>
+          <t>Demand evidence level is disclosed; SERP-only evidence is not treated as volume proof.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L019; R001-QA-L020</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6273,12 +6012,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>SEO title is natural, specific and within limit (56 chars).</t>
+          <t>meta_title_seo length=56; length alone does not prove semantic quality.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -6315,12 +6054,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Product title/H1 proposal is natural, specific and within limit (56 chars).</t>
+          <t>Product title is checked for presence; semantic correctness still depends on independent product review.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
@@ -6357,12 +6096,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Meta description is specific, product-tied and within Shopify limit (98 chars).</t>
+          <t>meta_description_seo length=98.</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -6399,12 +6138,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Product description is tied to visible design details and avoids unsupported claims targeted by QA.</t>
+          <t>HTML description must be present and free of internal process notes.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -6417,15 +6156,15 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6434,19 +6173,19 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Derived from 7 image rows; contact sheet/local evidence confirms image observations and alt relevance.</t>
+          <t>Traceability requires evidence id, fact-to-source map and revision.</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -6459,11 +6198,11 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
@@ -6476,26 +6215,22 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Source workbook hash, revision log, product evidence and image rows are traceable for this R001 snapshot.</t>
+          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L019; R001-QA-L020</t>
-        </is>
-      </c>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
@@ -6519,7 +6254,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="41" customWidth="1" min="10" max="10"/>
     <col width="41" customWidth="1" min="11" max="11"/>
@@ -6694,12 +6429,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6760,7 +6495,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/f22f6542b6c31065d5c01c931219593558543db1452783132e53b25ec93ac91f.jpg?v=1784384201</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6533,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -6864,7 +6599,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/ff5ee0cbe8d05a6b14d7c997f290ba42d6970721e4d58cf5e12e2549802041be.jpg?v=1784384202</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -6902,12 +6637,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6968,7 +6703,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/91bf92067c75307daea091393b28bc513132e4d3c3b3cbbae4f781d4906d8415.jpg?v=1784384207</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7006,12 +6741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7072,7 +6807,7 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/865fdc132abd37521e9fc32d02825e058f944d29cf0a290c530eaa530d5ed736.jpg?v=1784384207</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7110,12 +6845,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7176,7 +6911,7 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/2094179efd1dbfebe46459c055609668c55c864230ea9675f6250b3a6b332673.jpg?v=1784384213</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7214,12 +6949,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7280,7 +7015,7 @@
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/ec7d2a67f3d322550aa44434e78b81296b99ca2a5423818096610d51afd0fca2.jpg?v=1784384213</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7053,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,7 +7119,7 @@
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/d45b57fceb170f96d36200e6214d15d891baa91a6fec10ed6036e14457844e3c.jpg?v=1784384218</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7422,12 +7157,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7488,7 +7223,7 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/874c1407f741582553c7519d578f7485f356dd6ec01d2abe617acd47f3e6e918.jpg?v=1784384218</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7261,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7592,7 +7327,7 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/55ff57fbb545beed5c3b0cfc82842ffc940e03ae4b0e7a23582eb8540053ff99.jpg?v=1784375519</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7630,12 +7365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7696,7 +7431,7 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/46d8d748966c79876e5599313dd1fb4c6f3319dfb9ba412f96554df9db7559e3.jpg?v=1784375525</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7469,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7800,7 +7535,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/172423e8f61d8129b0414dcb14bb618e13d80e36d5f26fd8439b50590f48f441.jpg?v=1784375525</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7838,12 +7573,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7904,7 +7639,7 @@
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/a84cf45ea1f2a0cadde223334495455331b1e71c842c297091946ced593b262e.jpg?v=1784375530</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7677,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8008,7 +7743,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/a169ef5e1c64be03fd56c8ddead8934785acc3f20161140c0a66ace74d48882a.jpg?v=1784375530</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8046,12 +7781,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8112,7 +7847,7 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/73889b892b543f1f215dda40f69e294917f64cebe3419f9ad05eedc956733ac8.jpg?v=1784375535</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8150,12 +7885,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8216,7 +7951,7 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/bb612050d5c30e6eee1e64e41ac7e5769a8fceb4ae51bcc0fed560a3a268b9cc.jpg?v=1784375535</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8254,12 +7989,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8320,7 +8055,7 @@
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/0cf1acf9d14a6bae6bda1b8a6b27da8d33ef56f7b13ba3e07e911e0dc072fa7c.jpg?v=1784375540</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8093,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8424,7 +8159,7 @@
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/dffb4853e4eda6e21b75daf6432adee7834c72d2b04cfe0e7ac4aa89d183812d.jpg?v=1784375033</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8197,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8528,7 +8263,7 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/a39af69f623cd0fe9f8f5ea6c57650ba58f4853885bb316ce38da3826a90cf23.jpg?v=1784375033</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8566,12 +8301,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8632,7 +8367,7 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/cc3666595db44134459016bf4f1794a59723a422f7e306e17970d1225614b316.jpg?v=1784375038</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8670,12 +8405,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8736,7 +8471,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/323ba8595b71dd3513869167a9f4cb0e469d037058a798bf30facdefa49970bb.jpg?v=1784375038</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8509,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8840,7 +8575,7 @@
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/207ba3c754c89245bb6634f17800adfbfc96ee65bbce16b3b665c51c4c4aa2a5.jpg?v=1784375043</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8878,12 +8613,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8944,7 +8679,7 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/5eba5ebe8ca69a8bfe20bddbe9c7e8710d1bde3e926316a2eb61deb6d99396aa.jpg?v=1784375043</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -8982,12 +8717,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9048,7 +8783,7 @@
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/abfd6d9c154026773b9289faab95bc0d6a6c3e8fdc09a1ffa338cf63187ae3e4.jpg?v=1784375048</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9086,12 +8821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9152,7 +8887,7 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/19abf9486b413ff700367071a55655dc8738d7d173e70f18c4947865aea18752.jpg?v=1784375049</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9190,12 +8925,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9256,7 +8991,7 @@
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/ca37454e353d8e11c1fc2fec18de988b83582a6a70a762e5c6ebe70ca13d5903.jpg?v=1784383496</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9029,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9360,7 +9095,7 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/d11f511cedcb26bfd763f0867cd1e07027dc6d7f7facf26e470482cd36c4811e.jpg?v=1784383498</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9398,12 +9133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9464,7 +9199,7 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/2bb13e26d5f71d5108c137543460b6cfe5ec7b09e17ff583504b310cfb742d25.jpg?v=1784383501</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9237,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9568,7 +9303,7 @@
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/68579f756e106b93abce481692645b0638687a86df6086a52c6a9b79157cc1a2.jpg?v=1784383503</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9341,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9672,7 +9407,7 @@
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/c89187667d8c69ea1a335203c68b11e5987fbd0c1f73f2e529141b57c6719560.jpg?v=1784383507</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9445,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9776,7 +9511,7 @@
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/c8250fa083d8fc1bdbc3c1529f3818114a32c0cdd50af4da882d4a0de22987a8.jpg?v=1784383441</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9549,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9880,7 +9615,7 @@
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/daa0636622a7d236def2e8879b572ceca3735bf859d1b5327d9fe5989d043ce9.jpg?v=1784383441</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -9918,12 +9653,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9984,7 +9719,7 @@
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/84f5506257097283b8fef62c81663bfed9ad017820222cb9ab4a03a2d0a9d503.jpg?v=1784383447</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10022,12 +9757,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10088,7 +9823,7 @@
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/1cfd744f317704dd135ae51bf77139eb425950e31d874e210a244ac0384d18d0.jpg?v=1784383447</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10126,12 +9861,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10192,7 +9927,7 @@
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/c3a9202a6918fbf47a4fa7ee59a9bc3ab055531f402943cf387548c422aa0397.jpg?v=1784383452</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10230,12 +9965,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10296,7 +10031,7 @@
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/ac6097a39d18939b819c60f178d80396b34660c377e6db5539f927f3f1ee02ca.jpg?v=1784383425</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10069,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10400,7 +10135,7 @@
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/c6d670fa2a396c1f4c601a5ff96a3216663333e7d6d74149121fcfd6bc52b2ae.jpg?v=1784383430</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10173,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10504,7 +10239,7 @@
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/86dfddc396b7cbdb595b87786a1bc18e4ac702ad2de9f9d7e5934acf103c7e94.jpg?v=1784383430</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10542,12 +10277,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10608,7 +10343,7 @@
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/31f82a3a606183f237ed63da029546267a740df00b7f2612a696cd9ac6e16106.jpg?v=1784383436</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10381,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10712,7 +10447,7 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/9dbf77d4cb70b3028a54f480b4098c713af4a16ec323a3e22ea726a56f45db31.jpg?v=1784383436</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10750,12 +10485,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10816,7 +10551,7 @@
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/dbb9b1dd6389bd5c151ee03418b85329d0b13f1af89936c55bd44a7e3276c9fd.jpg?v=1784383386</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10589,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10920,7 +10655,7 @@
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/ed3aab7867649a62a2193475dc41bf75f3cfed0735894818046e34c0d1152156.jpg?v=1784383386</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -10958,12 +10693,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11024,7 +10759,7 @@
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/2e964ac6db8a47711615a091ba9d758910ea9af26713f5cff598a083697d8b88.jpg?v=1784383391</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11062,12 +10797,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11128,7 +10863,7 @@
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/b20ac371b2f6ec14f4abd8d3502e95bea4797196974e90bb4f55b520feb39ba9.jpg?v=1784383392</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11166,12 +10901,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11232,7 +10967,7 @@
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/ba2c8ed578ec8ec7d09a3b9110caf83b3f4fa552a4a53f087279f01944ac9c69.jpg?v=1784383397</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11005,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11336,7 +11071,7 @@
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/09c4c2a935e0bf0872c38534a3b08592c2b24b74bf33d5f97e868753c73d5300.jpg?v=1784383370</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11374,12 +11109,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11440,7 +11175,7 @@
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/39c90b8728413e116d09e2cc1092c6ecd1facc09d656631d32423b391fca84a6.jpg?v=1784383375</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11478,12 +11213,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11544,7 +11279,7 @@
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/3dc5325e587c423a4c5663fe30ff6f9a4c59ac8c83ecedc2b4a40e631e1b5e94.jpg?v=1784383375</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11582,12 +11317,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11648,7 +11383,7 @@
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/2536b0150906d9e10047d0a8ffd468a797a8e9318967dd2681298707deb2f5cb.jpg?v=1784383381</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11686,12 +11421,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11752,7 +11487,7 @@
       <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/354e2c4dc97778507ffa78131abf58c3e9f83c8f579777e7fffdc17ce313173e.jpg?v=1784383381</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11790,12 +11525,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -11856,7 +11591,7 @@
       <c r="W51" s="2" t="inlineStr"/>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/688074df088e163177ae937fe902b95452b64b1656f4a0ca176c405fd16828b7.jpg?v=1784383342</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11894,12 +11629,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -11960,7 +11695,7 @@
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/b01ad1958215cefea4f870fc0e726ae24afd95341f87d53bf79a1b2203a1d9ea.jpg?v=1784383348</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11733,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12064,7 +11799,7 @@
       <c r="W53" s="2" t="inlineStr"/>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/0ed60e39b57a01049da86a9536eee55de6e33e1709724cf3cd748ad0b6979b8f.jpg?v=1784383348</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12102,12 +11837,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12168,7 +11903,7 @@
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/8ab0774bcd3179b92ad222ffd9ee6344312b794bcdad45957b3b56e8b1d6a2a7.jpg?v=1784383353</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12206,12 +11941,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12272,7 +12007,7 @@
       <c r="W55" s="2" t="inlineStr"/>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/033f36d0cbfc1f9b15311dba0ee3f4b4329d7d69af46b0efe774f8be473ea918.jpg?v=1784383353</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12310,12 +12045,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -12376,7 +12111,7 @@
       <c r="W56" s="2" t="inlineStr"/>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/c7b38b2c6597d789e91c3ac6de899b13ab6f5e27b1bb864bb3714f9d62d9facd.jpg?v=1784383314</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12414,12 +12149,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -12480,7 +12215,7 @@
       <c r="W57" s="2" t="inlineStr"/>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/b420e1944db3b5667f43e8da5a3335383a6b9bbf18d52dca6e50f06b07ba047b.jpg?v=1784383319</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12518,12 +12253,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -12584,7 +12319,7 @@
       <c r="W58" s="2" t="inlineStr"/>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/5006a4056877053ce0914b5dd626f50227a18c78a9a5b169ee463794d1eea7b3.jpg?v=1784383319</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12622,12 +12357,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -12688,7 +12423,7 @@
       <c r="W59" s="2" t="inlineStr"/>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/0226cae5ede9a9e80886fa3626fb853dd2609aaa9e0474e840ba424219c4dc36.jpg?v=1784383325</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12726,12 +12461,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -12792,7 +12527,7 @@
       <c r="W60" s="2" t="inlineStr"/>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/54b27063638744d2a798f13281ca12f0e88de7aaf0fa77ff8be03c5c880567d4.jpg?v=1784383325</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12565,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -12896,7 +12631,7 @@
       <c r="W61" s="2" t="inlineStr"/>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/d33aec5b61afb909ac0f1f580928a13bd0ad94a9fcd67ec45503efaa77c6d3fd.jpg?v=1784377982</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -12934,12 +12669,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -13000,7 +12735,7 @@
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/591ad326ca56e2146255a82704352035b085a94cb19ef92eb351406c41ba50d2.jpg?v=1784377987</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -13038,12 +12773,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -13104,7 +12839,7 @@
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/144a52132e76f3622af43958a84749bac7b290422462f8fdb4a67fd3dbb72571.jpg?v=1784377988</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -13142,12 +12877,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -13208,7 +12943,7 @@
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/3844922a129bfdd34fb85f86f071a0f50663f4d9d4cc2ab76f6eecf3d2ca42e5.jpg?v=1784377992</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -13246,12 +12981,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -13312,7 +13047,7 @@
       <c r="W65" s="2" t="inlineStr"/>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/bc60bdddf88a758b3148d455e97a4b672850ddc1759173952243e1b2f71d3d40.jpg?v=1784377993</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13085,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -13416,7 +13151,7 @@
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/0d72f234aba151cc72c9e08eb2a1009514420a36180d339156683bca7ea5a4ed.jpg?v=1784377998</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -13454,12 +13189,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>CONTACT_SHEET_AND_LOCAL_EVIDENCE_RECHECK</t>
+          <t>INDEPENDENT_REVIEW_JSON</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:40:18+07:00</t>
+          <t>2026-09-08T11:08:40+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -13520,7 +13255,7 @@
       <c r="W67" s="2" t="inlineStr"/>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001; image_url:https://cdn.shopify.com/s/files/1/1023/0068/0561/files/affa299375e600d6f593fba55882dc1a7821f7623d000a80c6c2449a6ca1dc50.jpg?v=1784377999</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
         </is>
       </c>
     </row>
@@ -13536,20 +13271,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
-    <col width="68" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13606,1026 +13341,6 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>recheck_condition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support soccer 2026 rugs, soccer trophy area rugs, championship round rugs, personalized dog welcome mats, custom pet photo doormats and multi-pet entryway rugs. B033 separates near-duplicate soccer products by shape, stadium/trophy/host-flag motif, and dog products by phrase, number of pets and photo/name personalization.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520; evidence_id:B033-322; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>personalized-dog-doormat-custom-text-non-slip-c76f704530</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support personalized dog doormats, custom pet name welcome mats, custom pet photo mats, Halloween dog doormats, horse door mats and equestrian welcome rugs. B034 separates dog designs by exact phrase, pet count, Halloween motif and custom photo/name treatment; horse designs are separated by floral sunset versus fire-horse artwork.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>personalized-dog-doormat-custom-text-non-slip-c76f704530</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/personalized-dog-doormat-custom-text-non-slip-c76f704530; evidence_id:B034-338; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support running horse rugs, western horse doormats, equestrian area rugs, horse lover welcome mats, wolf rugs, galaxy wolf rugs and wolf welcome mats. B035 separates similar horse products by visible art style and color story, and separates wolf products by pack/moon, fire-ice, neon galaxy, monochrome forest and lightning snow motifs.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42; evidence_id:B035-346; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolves-welcome-mat-f320a33157</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support running horse rugs, western horse doormats, equestrian area rugs, horse lover welcome mats, wolf rugs, galaxy wolf rugs and wolf welcome mats. B035 separates similar horse products by visible art style and color story, and separates wolf products by pack/moon, fire-ice, neon galaxy, monochrome forest and lightning snow motifs.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolves-welcome-mat-f320a33157</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-f320a33157; evidence_id:B035-350; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support kids road map rugs, city road play rugs, washable kids playroom rugs, wolf area rugs, wolf bedroom rugs, galaxy wolf rugs and wolf welcome mats. B036 separates the road-map product by educational/playroom intent and separates similar wolf products by visual motif: foggy forest, blue moon lake, tribal medallion, floral line art, sepia wolf pack, snowy close-up, dreamcatcher, blue moon mountains and two-tone galaxy wolf.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; evidence_id:B036-352; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support kids road map rugs, city road play rugs, washable kids playroom rugs, wolf area rugs, wolf bedroom rugs, galaxy wolf rugs and wolf welcome mats. B036 separates the road-map product by educational/playroom intent and separates similar wolf products by visual motif: foggy forest, blue moon lake, tribal medallion, floral line art, sepia wolf pack, snowy close-up, dreamcatcher, blue moon mountains and two-tone galaxy wolf.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; evidence_id:B036-355; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolf-welcome-mat-0e4d706227</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support kids road map rugs, city road play rugs, washable kids playroom rugs, wolf area rugs, wolf bedroom rugs, galaxy wolf rugs and wolf welcome mats. B036 separates the road-map product by educational/playroom intent and separates similar wolf products by visual motif: foggy forest, blue moon lake, tribal medallion, floral line art, sepia wolf pack, snowy close-up, dreamcatcher, blue moon mountains and two-tone galaxy wolf.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>custom-galaxy-wolf-welcome-mat-0e4d706227</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; evidence_id:B036-356; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support kids road map rugs, city road play rugs, washable kids playroom rugs, wolf area rugs, wolf bedroom rugs, galaxy wolf rugs and wolf welcome mats. B036 separates the road-map product by educational/playroom intent and separates similar wolf products by visual motif: foggy forest, blue moon lake, tribal medallion, floral line art, sepia wolf pack, snowy close-up, dreamcatcher, blue moon mountains and two-tone galaxy wolf.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; evidence_id:B036-358; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support kids road map rugs, city road play rugs, washable kids playroom rugs, wolf area rugs, wolf bedroom rugs, galaxy wolf rugs and wolf welcome mats. B036 separates the road-map product by educational/playroom intent and separates similar wolf products by visual motif: foggy forest, blue moon lake, tribal medallion, floral line art, sepia wolf pack, snowy close-up, dreamcatcher, blue moon mountains and two-tone galaxy wolf.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; evidence_id:B036-360; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>custom-dog-paw-print-shaped-rug-39afbc78d5</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace and retail SERPs support galaxy wolf rugs, wolf bedroom rugs, paw print rugs, bear paw shaped rugs, dog paw rugs, cabin/lodge paw decor, kids road map rugs and city car play rugs. B037 separates similar paw-shaped rugs by animal intent and visible pattern/color, while the two road-map products are separated by map layout and playroom/classroom use.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Keyword evidence is SERP-only/no paid volume; this is acceptable as disclosed but not demand-volume proof.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>No paid volume or first-party demand source in workbook.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Optional: add Search Console, internal search or paid keyword source before human approval if required.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Human reviewer accepts SERP-only evidence or adds stronger source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>R001-QA-L020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>custom-dog-paw-print-shaped-rug-39afbc78d5</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>LIMITATION</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>admin_export/media_ids</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Storefront/public CDN evidence is enough for content QA, but admin/export values are still needed before deploy payload.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Image_Audit rows still include media_export_url_unknown_without_shopify_export.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Before deploy, export Shopify/Matrixify and verify product/media IDs and current admin SEO values.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>source_workbook_sha256:5caf7f824142c9523e922b08feebfd3fd5e09a475f585177d21a17d1f45fad97; product_url:https://chillgen.com/products/custom-dog-paw-print-shaped-rug-39afbc78d5; evidence_id:B037-363; contact_sheet:/Users/buiquanghuy/Documents/seo_chillgen/seo_runs/chillgen.com/chillgen_20260907_01/revisions/R001_contact_sheet.jpg; revision_log:R001</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Admin/export reconciliation completed before approval/deploy.</t>
         </is>
       </c>
     </row>

--- a/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/SEO_QA_REV_R001.xlsx
+++ b/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/SEO_QA_REV_R001.xlsx
@@ -872,7 +872,7 @@
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>CHECKED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Image score is derived only from independent per-image ratings; workbook metadata alone is not visual QA.</t>
+          <t>Derived as 0.20 × average per-image verified points and assessed weight.</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_01</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_02</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_03</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_04</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_05</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_06</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_07</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B033-322; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-soccer-tournament-trophy-area-rug-8d23acd520-8d23acd520__img_08</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_01</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_02</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_03</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_04</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7743,7 +7743,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_05</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_06</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_07</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_08</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_09</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_10</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8367,7 +8367,7 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_11</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8471,7 +8471,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_12</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_13</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8679,7 +8679,7 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_14</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_15</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B034-338; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:personalized-dog-doormat-custom-text-non-slip-c76f704530__img_16</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42__img_01</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9095,7 +9095,7 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42__img_02</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9199,7 +9199,7 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42__img_03</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42__img_04</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-346; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-bedroom-living-room-eb7c237d42-eb7c237d42__img_05</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-welcome-mat-f320a33157__img_01</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9615,7 +9615,7 @@
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-welcome-mat-f320a33157__img_02</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9719,7 +9719,7 @@
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-welcome-mat-f320a33157__img_03</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9823,7 +9823,7 @@
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-welcome-mat-f320a33157__img_04</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B035-350; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-welcome-mat-f320a33157__img_05</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10031,7 +10031,7 @@
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_01</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_02</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10239,7 +10239,7 @@
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_03</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_04</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-352; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_05</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_01</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10655,7 +10655,7 @@
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_02</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_03</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10863,7 +10863,7 @@
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_04</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-355; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_05</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolf-welcome-mat-0e4d706227__img_01</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolf-welcome-mat-0e4d706227__img_02</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11279,7 +11279,7 @@
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolf-welcome-mat-0e4d706227__img_03</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolf-welcome-mat-0e4d706227__img_04</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-356; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-galaxy-wolf-welcome-mat-0e4d706227__img_05</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       <c r="W51" s="2" t="inlineStr"/>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_01</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -11695,7 +11695,7 @@
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_02</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       <c r="W53" s="2" t="inlineStr"/>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_03</t>
         </is>
       </c>
     </row>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -11903,7 +11903,7 @@
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_04</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12007,7 +12007,7 @@
       <c r="W55" s="2" t="inlineStr"/>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-358; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_05</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       <c r="W56" s="2" t="inlineStr"/>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_01</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       <c r="W57" s="2" t="inlineStr"/>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_02</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -12319,7 +12319,7 @@
       <c r="W58" s="2" t="inlineStr"/>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_03</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -12423,7 +12423,7 @@
       <c r="W59" s="2" t="inlineStr"/>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_04</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -12527,7 +12527,7 @@
       <c r="W60" s="2" t="inlineStr"/>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B036-360; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_05</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -12631,7 +12631,7 @@
       <c r="W61" s="2" t="inlineStr"/>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_01</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_02</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -12839,7 +12839,7 @@
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_03</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -12943,7 +12943,7 @@
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_04</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       <c r="W65" s="2" t="inlineStr"/>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_05</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_06</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:08:40+07:00</t>
+          <t>2026-09-08T11:22:10+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -13255,7 +13255,7 @@
       <c r="W67" s="2" t="inlineStr"/>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001</t>
+          <t>source_workbook_sha256:97db06b7c1459c44875c1da98c7c41043b338045d9140dd19d3bc84fd8a18edf; evidence_id:B037-363; revision_log:R001; independent_image_evidence:seo_runs/chillgen.com/chillgen_20260907_01/qa/QA-20260908-REV-R001/independent_evidence.json; image_key:custom-dog-paw-print-shaped-rug-39afbc78d5__img_07</t>
         </is>
       </c>
     </row>
